--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130644031</v>
+        <v>130644032</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452940</v>
+        <v>453098</v>
       </c>
       <c r="R2" t="n">
-        <v>7079819</v>
+        <v>7079756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130644032</v>
+        <v>130644031</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453098</v>
+        <v>452940</v>
       </c>
       <c r="R3" t="n">
-        <v>7079756</v>
+        <v>7079819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644013</v>
+        <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453074</v>
+        <v>452867</v>
       </c>
       <c r="R14" t="n">
-        <v>7079568</v>
+        <v>7079899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644030</v>
+        <v>130644029</v>
       </c>
       <c r="B15" t="n">
         <v>79209</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452867</v>
+        <v>452832</v>
       </c>
       <c r="R15" t="n">
-        <v>7079899</v>
+        <v>7079918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644029</v>
+        <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452832</v>
+        <v>453074</v>
       </c>
       <c r="R16" t="n">
-        <v>7079918</v>
+        <v>7079568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>130644021</v>
       </c>
       <c r="B4" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130644023</v>
       </c>
       <c r="B5" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130644022</v>
       </c>
       <c r="B6" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130644017</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130644020</v>
       </c>
       <c r="B9" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130644019</v>
       </c>
       <c r="B11" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>130644018</v>
       </c>
       <c r="B13" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644030</v>
+        <v>130644013</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452867</v>
+        <v>453074</v>
       </c>
       <c r="R14" t="n">
-        <v>7079899</v>
+        <v>7079568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644029</v>
+        <v>130644030</v>
       </c>
       <c r="B15" t="n">
         <v>79209</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452832</v>
+        <v>452867</v>
       </c>
       <c r="R15" t="n">
-        <v>7079918</v>
+        <v>7079899</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644013</v>
+        <v>130644029</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453074</v>
+        <v>452832</v>
       </c>
       <c r="R16" t="n">
-        <v>7079568</v>
+        <v>7079918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130644032</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130644031</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130644021</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130644023</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130644022</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130644017</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>130644014</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130644020</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130644028</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130644019</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130644027</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>130644018</v>
       </c>
       <c r="B13" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644013</v>
+        <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453074</v>
+        <v>452867</v>
       </c>
       <c r="R14" t="n">
-        <v>7079568</v>
+        <v>7079899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644030</v>
+        <v>130644029</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452867</v>
+        <v>452832</v>
       </c>
       <c r="R15" t="n">
-        <v>7079899</v>
+        <v>7079918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644029</v>
+        <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452832</v>
+        <v>453074</v>
       </c>
       <c r="R16" t="n">
-        <v>7079918</v>
+        <v>7079568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644030</v>
+        <v>130644013</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452867</v>
+        <v>453074</v>
       </c>
       <c r="R14" t="n">
-        <v>7079899</v>
+        <v>7079568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644029</v>
+        <v>130644030</v>
       </c>
       <c r="B15" t="n">
         <v>79211</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452832</v>
+        <v>452867</v>
       </c>
       <c r="R15" t="n">
-        <v>7079918</v>
+        <v>7079899</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644013</v>
+        <v>130644029</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453074</v>
+        <v>452832</v>
       </c>
       <c r="R16" t="n">
-        <v>7079568</v>
+        <v>7079918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644013</v>
+        <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453074</v>
+        <v>452867</v>
       </c>
       <c r="R14" t="n">
-        <v>7079568</v>
+        <v>7079899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644030</v>
+        <v>130644029</v>
       </c>
       <c r="B15" t="n">
         <v>79211</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452867</v>
+        <v>452832</v>
       </c>
       <c r="R15" t="n">
-        <v>7079899</v>
+        <v>7079918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644029</v>
+        <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452832</v>
+        <v>453074</v>
       </c>
       <c r="R16" t="n">
-        <v>7079918</v>
+        <v>7079568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130644032</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130644031</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130644021</v>
       </c>
       <c r="B4" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130644023</v>
       </c>
       <c r="B5" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130644022</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130644017</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>130644014</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130644020</v>
       </c>
       <c r="B9" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130644028</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130644019</v>
       </c>
       <c r="B11" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130644027</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>130644018</v>
       </c>
       <c r="B13" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>130644029</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130644032</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130644031</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130644021</v>
       </c>
       <c r="B4" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130644023</v>
       </c>
       <c r="B5" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130644022</v>
       </c>
       <c r="B6" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130644017</v>
       </c>
       <c r="B7" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>130644014</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130644020</v>
       </c>
       <c r="B9" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130644028</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130644019</v>
       </c>
       <c r="B11" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130644027</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>130644018</v>
       </c>
       <c r="B13" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>130644029</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130644032</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130644031</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130644021</v>
       </c>
       <c r="B4" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>130644023</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>130644022</v>
       </c>
       <c r="B6" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>130644017</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>130644014</v>
       </c>
       <c r="B8" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130644020</v>
       </c>
       <c r="B9" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>130644028</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130644019</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>130644027</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>130644018</v>
       </c>
       <c r="B13" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644030</v>
+        <v>130644013</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452867</v>
+        <v>453074</v>
       </c>
       <c r="R14" t="n">
-        <v>7079899</v>
+        <v>7079568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644029</v>
+        <v>130644030</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452832</v>
+        <v>452867</v>
       </c>
       <c r="R15" t="n">
-        <v>7079918</v>
+        <v>7079899</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644013</v>
+        <v>130644029</v>
       </c>
       <c r="B16" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453074</v>
+        <v>452832</v>
       </c>
       <c r="R16" t="n">
-        <v>7079568</v>
+        <v>7079918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 59359-2025 artfynd.xlsx
+++ b/artfynd/A 59359-2025 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130644013</v>
+        <v>130644030</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453074</v>
+        <v>452867</v>
       </c>
       <c r="R14" t="n">
-        <v>7079568</v>
+        <v>7079899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130644030</v>
+        <v>130644029</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452867</v>
+        <v>452832</v>
       </c>
       <c r="R15" t="n">
-        <v>7079899</v>
+        <v>7079918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130644029</v>
+        <v>130644013</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2051,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452832</v>
+        <v>453074</v>
       </c>
       <c r="R16" t="n">
-        <v>7079918</v>
+        <v>7079568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
